--- a/sheets/조재수대금교본/검수/적성가.xlsx
+++ b/sheets/조재수대금교본/검수/적성가.xlsx
@@ -4995,13 +4995,13 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -5013,7 +5013,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∨
+          <t xml:space="preserve">湳
 㳞㴌
 㳞</t>
         </is>
@@ -5021,7 +5021,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -5040,42 +5040,27 @@
         <is>
           <t xml:space="preserve">汰應∼
 –
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-ﾉ
-‹‹</t>
-        </is>
-      </c>
+      <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –
-–南
-‹</t>
+–南</t>
         </is>
       </c>
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ﾉ
+          <t xml:space="preserve">汰
 應
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K4" s="23"/>
@@ -5083,16 +5068,11 @@
         <is>
           <t xml:space="preserve">㳞㴌
 㳞
-汰
-ﾉ</t>
+汰</t>
         </is>
       </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N4" s="21"/>
       <c r="O4" s="23"/>
     </row>
     <row r="5" ht="145.5" customHeight="true">
@@ -5108,7 +5088,6 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-ﾉ
 㴌
 –</t>
         </is>
@@ -5140,8 +5119,7 @@
         <is>
           <t xml:space="preserve">應∼
 –南
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="M5" s="24"/>
@@ -5160,11 +5138,7 @@
       <c r="C6" s="22"/>
       <c r="D6" s="21"/>
       <c r="E6" s="22"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="22"/>
       <c r="H6" s="21"/>
       <c r="I6" s="22"/>
@@ -5187,11 +5161,7 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21"/>
       <c r="G7" s="23"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H7" s="21"/>
       <c r="I7" s="23"/>
       <c r="J7" s="21"/>
       <c r="K7" s="23"/>
@@ -5202,39 +5172,28 @@
     </row>
     <row r="8" ht="145.5" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∧
-㳞
-–
-‹</t>
+          <t xml:space="preserve">㳞
+–</t>
         </is>
       </c>
       <c r="E8" s="24"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌
 應∼
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應∧
+          <t xml:space="preserve">應
 汰
 △</t>
         </is>
@@ -5261,9 +5220,8 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽
-–
-И</t>
+          <t xml:space="preserve">湳
+–</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -5271,15 +5229,14 @@
         <is>
           <t xml:space="preserve">㴌∼
 –
-湳
-‹</t>
+湳</t>
         </is>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-–湳∽
+–湳
 㳞</t>
         </is>
       </c>
@@ -5294,20 +5251,19 @@
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="O9" s="22"/>
@@ -5316,31 +5272,23 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕∧∼
-‹</t>
+          <t xml:space="preserve">潕∼</t>
         </is>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕∼
-‹</t>
+          <t xml:space="preserve">潕∼</t>
         </is>
       </c>
       <c r="E10" s="23"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰應
 –∼
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -5348,24 +5296,17 @@
         <is>
           <t xml:space="preserve">㳞㴌
 㳞
-汰
-ﾉ‹</t>
+汰</t>
         </is>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –湳
-㳞
-ﾉ‹</t>
+㳞</t>
         </is>
       </c>
       <c r="O10" s="23"/>
@@ -5374,20 +5315,19 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-Z
 –</t>
         </is>
       </c>
@@ -5402,15 +5342,13 @@
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲∼
-‹</t>
+          <t xml:space="preserve">仲∼</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -5427,26 +5365,16 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D12" s="21"/>
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-–
-汰
-ﾉ</t>
+          <t xml:space="preserve">–
+汰</t>
         </is>
       </c>
       <c r="G12" s="22"/>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H12" s="21"/>
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
@@ -5456,8 +5384,7 @@
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-ﾉ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -5478,7 +5405,7 @@
         <is>
           <t xml:space="preserve">㳞㴌
 湳㳞
-⊏∼
+∼
 –</t>
         </is>
       </c>
@@ -5495,7 +5422,7 @@
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="M13" s="23"/>
@@ -5518,8 +5445,7 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∼
-‹</t>
+          <t xml:space="preserve">㴌∼</t>
         </is>
       </c>
       <c r="E14" s="24"/>
@@ -5543,7 +5469,7 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="M14" s="24"/>
@@ -5581,8 +5507,7 @@
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–
-И</t>
+–</t>
         </is>
       </c>
       <c r="E17" s="22"/>
@@ -5610,13 +5535,13 @@
       <c r="K17" s="22"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="O17" s="22"/>
@@ -5627,8 +5552,7 @@
       <c r="C18" s="23"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕∧∼
-‹</t>
+          <t xml:space="preserve">潕∼</t>
         </is>
       </c>
       <c r="E18" s="23"/>
@@ -5636,18 +5560,11 @@
         <is>
           <t xml:space="preserve">汰應
 –
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G18" s="23"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="H18" s="21"/>
       <c r="I18" s="23"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
@@ -5657,21 +5574,9 @@
         </is>
       </c>
       <c r="K18" s="23"/>
-      <c r="L18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-ﾉ
-‹‹</t>
-        </is>
-      </c>
+      <c r="L18" s="21"/>
       <c r="M18" s="23"/>
-      <c r="N18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="N18" s="21"/>
       <c r="O18" s="23"/>
     </row>
     <row r="19" ht="145.5" customHeight="true">
@@ -5680,7 +5585,7 @@
       <c r="C19" s="24"/>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E19" s="24"/>
@@ -5706,7 +5611,7 @@
       <c r="K19" s="24"/>
       <c r="L19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ㄴ潢ﾉ
+          <t xml:space="preserve">潢
 㴌
 –</t>
         </is>
@@ -5735,19 +5640,11 @@
       <c r="G20" s="22"/>
       <c r="H20" s="21"/>
       <c r="I20" s="22"/>
-      <c r="J20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J20" s="21"/>
       <c r="K20" s="22"/>
       <c r="L20" s="21"/>
       <c r="M20" s="22"/>
-      <c r="N20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N20" s="21"/>
       <c r="O20" s="22"/>
     </row>
     <row r="21" ht="145.5" customHeight="true">
@@ -5762,7 +5659,7 @@
       <c r="I21" s="23"/>
       <c r="J21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K21" s="23"/>
@@ -5783,40 +5680,28 @@
       <c r="E22" s="24"/>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧
+          <t xml:space="preserve">南
 應
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G22" s="24"/>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H22" s="21"/>
       <c r="I22" s="24"/>
       <c r="J22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∼
-‹</t>
+          <t xml:space="preserve">㴌∼</t>
         </is>
       </c>
       <c r="K22" s="24"/>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∧
-㳞
-–
-‹</t>
+          <t xml:space="preserve">㳞
+–</t>
         </is>
       </c>
       <c r="M22" s="24"/>
-      <c r="N22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N22" s="21"/>
       <c r="O22" s="24"/>
     </row>
     <row r="23" ht="145.5" customHeight="true">
@@ -5850,7 +5735,7 @@
       <c r="L23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-湳∽
+湳
 –</t>
         </is>
       </c>
@@ -5870,10 +5755,9 @@
       <c r="E24" s="23"/>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應∧
+          <t xml:space="preserve">應
 –南
-姑
-‹</t>
+姑</t>
         </is>
       </c>
       <c r="G24" s="23"/>
@@ -5881,17 +5765,15 @@
         <is>
           <t xml:space="preserve">㴌
 㳞
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I24" s="23"/>
       <c r="J24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
-㴌∧
-–∼
-‹</t>
+㴌
+–∼</t>
         </is>
       </c>
       <c r="K24" s="23"/>
@@ -5901,8 +5783,7 @@
         <is>
           <t xml:space="preserve">汰南
 汰
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="O24" s="23"/>
@@ -5931,7 +5812,7 @@
       <c r="I25" s="24"/>
       <c r="J25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∽</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K25" s="24"/>
@@ -5952,11 +5833,7 @@
       <c r="C26" s="22"/>
       <c r="D26" s="21"/>
       <c r="E26" s="22"/>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F26" s="21"/>
       <c r="G26" s="22"/>
       <c r="H26" s="21" t="inlineStr">
         <is>
@@ -5966,23 +5843,11 @@
         </is>
       </c>
       <c r="I26" s="22"/>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J26" s="21"/>
       <c r="K26" s="22"/>
-      <c r="L26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L26" s="21"/>
       <c r="M26" s="22"/>
-      <c r="N26" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N26" s="21"/>
       <c r="O26" s="22"/>
     </row>
     <row r="27" ht="145.5" customHeight="true">
@@ -5996,7 +5861,6 @@
       <c r="H27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-ﾉ
 㴌
 –</t>
         </is>
@@ -6029,11 +5893,7 @@
         </is>
       </c>
       <c r="G28" s="24"/>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H28" s="21"/>
       <c r="I28" s="24"/>
       <c r="J28" s="21" t="inlineStr">
         <is>
@@ -6045,8 +5905,7 @@
       <c r="K28" s="24"/>
       <c r="L28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M28" s="24"/>

--- a/sheets/조재수대금교본/검수/적성가.xlsx
+++ b/sheets/조재수대금교본/검수/적성가.xlsx
@@ -4995,13 +4995,13 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -5013,7 +5013,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">湳∨
 㳞㴌
 㳞</t>
         </is>
@@ -5021,7 +5021,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -5044,9 +5044,19 @@
         </is>
       </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+ﾉ</t>
+        </is>
+      </c>
       <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+ﾉ</t>
+        </is>
+      </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -5058,7 +5068,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰ﾉ
 應
 –</t>
         </is>
@@ -5068,7 +5078,8 @@
         <is>
           <t xml:space="preserve">㳞㴌
 㳞
-汰</t>
+汰
+ﾉ</t>
         </is>
       </c>
       <c r="M4" s="23"/>
@@ -5088,6 +5099,7 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
+ﾉ
 㴌
 –</t>
         </is>
@@ -5138,7 +5150,11 @@
       <c r="C6" s="22"/>
       <c r="D6" s="21"/>
       <c r="E6" s="22"/>
-      <c r="F6" s="21"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21"/>
       <c r="I6" s="22"/>
@@ -5176,7 +5192,8 @@
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">Z∧
+㳞
 –</t>
         </is>
       </c>
@@ -5193,7 +5210,7 @@
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
+          <t xml:space="preserve">應∧
 汰
 △</t>
         </is>
@@ -5220,8 +5237,9 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-–</t>
+          <t xml:space="preserve">湳∽
+–
+И</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -5236,7 +5254,7 @@
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-–湳
+–湳∽
 㳞</t>
         </is>
       </c>
@@ -5251,13 +5269,13 @@
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="M9" s="22"/>
@@ -5272,7 +5290,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕∼</t>
+          <t xml:space="preserve">潕∧∼</t>
         </is>
       </c>
       <c r="C10" s="23"/>
@@ -5282,7 +5300,11 @@
         </is>
       </c>
       <c r="E10" s="23"/>
-      <c r="F10" s="21"/>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
@@ -5296,17 +5318,23 @@
         <is>
           <t xml:space="preserve">㳞㴌
 㳞
-汰</t>
+汰
+ﾉ</t>
         </is>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="21"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –湳
-㳞</t>
+㳞
+ﾉ</t>
         </is>
       </c>
       <c r="O10" s="23"/>
@@ -5315,19 +5343,20 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
+Z
 –</t>
         </is>
       </c>
@@ -5369,12 +5398,18 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-汰</t>
+          <t xml:space="preserve">Z
+–
+汰
+ﾉ</t>
         </is>
       </c>
       <c r="G12" s="22"/>
-      <c r="H12" s="21"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
@@ -5384,7 +5419,8 @@
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳
+ﾉ</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -5405,7 +5441,7 @@
         <is>
           <t xml:space="preserve">㳞㴌
 湳㳞
-∼
+⊏∼
 –</t>
         </is>
       </c>
@@ -5422,7 +5458,7 @@
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="M13" s="23"/>
@@ -5469,7 +5505,7 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">Z∼</t>
         </is>
       </c>
       <c r="M14" s="24"/>
@@ -5507,7 +5543,8 @@
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–</t>
+–
+И</t>
         </is>
       </c>
       <c r="E17" s="22"/>
@@ -5535,13 +5572,13 @@
       <c r="K17" s="22"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="O17" s="22"/>
@@ -5552,7 +5589,7 @@
       <c r="C18" s="23"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕∼</t>
+          <t xml:space="preserve">潕∧∼</t>
         </is>
       </c>
       <c r="E18" s="23"/>
@@ -5564,7 +5601,12 @@
         </is>
       </c>
       <c r="G18" s="23"/>
-      <c r="H18" s="21"/>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+ﾉ</t>
+        </is>
+      </c>
       <c r="I18" s="23"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
@@ -5574,9 +5616,19 @@
         </is>
       </c>
       <c r="K18" s="23"/>
-      <c r="L18" s="21"/>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+ﾉ</t>
+        </is>
+      </c>
       <c r="M18" s="23"/>
-      <c r="N18" s="21"/>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+ﾉ</t>
+        </is>
+      </c>
       <c r="O18" s="23"/>
     </row>
     <row r="19" ht="145.5" customHeight="true">
@@ -5585,7 +5637,7 @@
       <c r="C19" s="24"/>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="E19" s="24"/>
@@ -5611,7 +5663,7 @@
       <c r="K19" s="24"/>
       <c r="L19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">ㄴ潢ﾉ
 㴌
 –</t>
         </is>
@@ -5644,7 +5696,11 @@
       <c r="K20" s="22"/>
       <c r="L20" s="21"/>
       <c r="M20" s="22"/>
-      <c r="N20" s="21"/>
+      <c r="N20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O20" s="22"/>
     </row>
     <row r="21" ht="145.5" customHeight="true">
@@ -5659,7 +5715,7 @@
       <c r="I21" s="23"/>
       <c r="J21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="K21" s="23"/>
@@ -5680,7 +5736,7 @@
       <c r="E22" s="24"/>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南∧
 應
 –</t>
         </is>
@@ -5696,7 +5752,8 @@
       <c r="K22" s="24"/>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">Z∧
+㳞
 –</t>
         </is>
       </c>
@@ -5735,7 +5792,7 @@
       <c r="L23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-湳
+湳∽
 –</t>
         </is>
       </c>
@@ -5755,7 +5812,7 @@
       <c r="E24" s="23"/>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
+          <t xml:space="preserve">應∧
 –南
 姑</t>
         </is>
@@ -5772,7 +5829,7 @@
       <c r="J24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
-㴌
+㴌∧
 –∼</t>
         </is>
       </c>
@@ -5812,7 +5869,7 @@
       <c r="I25" s="24"/>
       <c r="J25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∽</t>
         </is>
       </c>
       <c r="K25" s="24"/>
@@ -5833,7 +5890,11 @@
       <c r="C26" s="22"/>
       <c r="D26" s="21"/>
       <c r="E26" s="22"/>
-      <c r="F26" s="21"/>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G26" s="22"/>
       <c r="H26" s="21" t="inlineStr">
         <is>
@@ -5843,11 +5904,19 @@
         </is>
       </c>
       <c r="I26" s="22"/>
-      <c r="J26" s="21"/>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K26" s="22"/>
       <c r="L26" s="21"/>
       <c r="M26" s="22"/>
-      <c r="N26" s="21"/>
+      <c r="N26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O26" s="22"/>
     </row>
     <row r="27" ht="145.5" customHeight="true">
@@ -5861,6 +5930,7 @@
       <c r="H27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
+ﾉ
 㴌
 –</t>
         </is>

--- a/sheets/조재수대금교본/검수/적성가.xlsx
+++ b/sheets/조재수대금교본/검수/적성가.xlsx
@@ -4943,26 +4943,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="97.56" customHeight="true">
+    <row r="2" ht="83.33" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="145.5" customHeight="true">
+    <row r="3" ht="124.21" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="145.5" customHeight="true">
+    <row r="4" ht="124.21" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       <c r="N4" s="21"/>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="145.5" customHeight="true">
+    <row r="5" ht="124.21" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="O5" s="24"/>
     </row>
-    <row r="6" ht="145.5" customHeight="true">
+    <row r="6" ht="124.21" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -5169,7 +5169,7 @@
       <c r="N6" s="21"/>
       <c r="O6" s="22"/>
     </row>
-    <row r="7" ht="145.5" customHeight="true">
+    <row r="7" ht="124.21" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -5186,7 +5186,7 @@
       <c r="N7" s="21"/>
       <c r="O7" s="23"/>
     </row>
-    <row r="8" ht="145.5" customHeight="true">
+    <row r="8" ht="124.21" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="O8" s="24"/>
     </row>
-    <row r="9" ht="145.5" customHeight="true">
+    <row r="9" ht="124.21" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" ht="145.5" customHeight="true">
+    <row r="10" ht="124.21" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="O10" s="23"/>
     </row>
-    <row r="11" ht="145.5" customHeight="true">
+    <row r="11" ht="124.21" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="O11" s="24"/>
     </row>
-    <row r="12" ht="145.5" customHeight="true">
+    <row r="12" ht="124.21" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" ht="145.5" customHeight="true">
+    <row r="13" ht="124.21" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="145.5" customHeight="true">
+    <row r="14" ht="124.21" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="97.56" customHeight="true">
+    <row r="16" ht="83.33" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
       <c r="N16" s="20"/>
       <c r="O16" s="20"/>
     </row>
-    <row r="17" ht="145.5" customHeight="true">
+    <row r="17" ht="124.21" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="O17" s="22"/>
     </row>
-    <row r="18" ht="145.5" customHeight="true">
+    <row r="18" ht="124.21" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O18" s="23"/>
     </row>
-    <row r="19" ht="145.5" customHeight="true">
+    <row r="19" ht="124.21" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="O19" s="24"/>
     </row>
-    <row r="20" ht="145.5" customHeight="true">
+    <row r="20" ht="124.21" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="O20" s="22"/>
     </row>
-    <row r="21" ht="145.5" customHeight="true">
+    <row r="21" ht="124.21" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -5724,7 +5724,7 @@
       <c r="N21" s="21"/>
       <c r="O21" s="23"/>
     </row>
-    <row r="22" ht="145.5" customHeight="true">
+    <row r="22" ht="124.21" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -5761,7 +5761,7 @@
       <c r="N22" s="21"/>
       <c r="O22" s="24"/>
     </row>
-    <row r="23" ht="145.5" customHeight="true">
+    <row r="23" ht="124.21" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="O23" s="22"/>
     </row>
-    <row r="24" ht="145.5" customHeight="true">
+    <row r="24" ht="124.21" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="O24" s="23"/>
     </row>
-    <row r="25" ht="145.5" customHeight="true">
+    <row r="25" ht="124.21" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="O25" s="24"/>
     </row>
-    <row r="26" ht="145.5" customHeight="true">
+    <row r="26" ht="124.21" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="O26" s="22"/>
     </row>
-    <row r="27" ht="145.5" customHeight="true">
+    <row r="27" ht="124.21" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -5949,7 +5949,7 @@
       <c r="N27" s="21"/>
       <c r="O27" s="23"/>
     </row>
-    <row r="28" ht="145.5" customHeight="true">
+    <row r="28" ht="124.21" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -5995,7 +5995,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="41"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="48"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
